--- a/output/batch_results.xlsx
+++ b/output/batch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,11 +563,6 @@
           <t>https://www.wildberries.ru/seller/45521</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/45521</t>
-        </is>
-      </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
@@ -588,33 +583,33 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
+          <t>PARTIAL_SUCCESS</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>ИНН найден на странице продавца</t>
+          <t>WB показал защиту, но часть реквизитов всё же извлечена</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>200</v>
+        <v>498</v>
       </c>
       <c r="S2" t="b">
         <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>C:\Users\Пользователь\Desktop\AdBeam\тест_парсер\artifacts\row_2.png</t>
+          <t>output\artifacts\row_2.png</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>C:\Users\Пользователь\Desktop\AdBeam\тест_парсер\artifacts\row_2.html</t>
+          <t>output\artifacts\row_2.html</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>C:\Users\Пользователь\Desktop\AdBeam\тест_парсер\artifacts\row_2_text.txt</t>
+          <t>output\artifacts\row_2_text.txt</t>
         </is>
       </c>
     </row>
@@ -699,17 +694,762 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>C:\Users\Пользователь\Desktop\AdBeam\тест_парсер\artifacts\row_3.png</t>
+          <t>output\artifacts\row_3.png</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>C:\Users\Пользователь\Desktop\AdBeam\тест_парсер\artifacts\row_3.html</t>
+          <t>output\artifacts\row_3.html</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>C:\Users\Пользователь\Desktop\AdBeam\тест_парсер\artifacts\row_3_text.txt</t>
+          <t>output\artifacts\row_3_text.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Утепленные брюки джоггеры на флисе</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>49113986</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bronks</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronks</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/49113986/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/267074</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/267074</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Все товары</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ИП</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>772845643657</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>321774600250048</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ИНН найден на странице продавца</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_4.png</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_4.html</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_4_text.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые со стрелками</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>140847156</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUITBASE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SUITBASE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/140847156/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1173982</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1173982</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Все товары</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ИП</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>280116974150</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>322527500073632</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ИНН найден на странице продавца</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_5.png</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_5.html</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_5_text.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Классический свадебный костюм тройка</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>296160661</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TOMMY HAAS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TOMMY HAAS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/296160661/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1191692</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1191692</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Все товары</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ИП</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>330109279380</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>323330000002501</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ИНН найден на странице продавца</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_6.png</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_6.html</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_6_text.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Брюки прямые чинос слаксы</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8317220</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Westrenger</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>WESTRENGER</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/8317220/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/29424</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/29424</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Все товары</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ООО</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>7723903462</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1147746325550</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ИНН найден на странице продавца</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>200</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_7.png</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_7.html</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_7_text.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Брюки чиносы весенние классические прямые</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>17596354</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Westrenger</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>WESTRANGER</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/17596354/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/93453</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/93453</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Все товары</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ИП</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>771878589629</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>319774600332200</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ИНН найден на странице продавца</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>200</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_8.png</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_8.html</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_8_text.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Костюм классический двойка серый в офис смокинг на свадьбу</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>147499497</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PAOLO MARK</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Paolo Mark</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/147499497/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/135762</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/135762</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Все товары</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ИП</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>503818349810</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>319508100111017</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ИНН найден на странице продавца</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_9.png</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_9.html</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_9_text.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Жилетка утепленная безрукавка с карманами</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>201057687</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Eberron</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Eberron</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/201057687/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/rivegauche</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/rivegauche</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Все товары</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SELLER_PAGE_OPENED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Перешли на страницу продавца, но реквизиты не извлеклись</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_10.png</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_10.html</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_10_text.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Классический деловой костюм двойка</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>412630283</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RIERA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Riera</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/412630283/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/520471</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/520471</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Все товары</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ИП</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>330106491275</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>321332800065130</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ИНН найден на странице продавца</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>200</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_11.png</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_11.html</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>output\artifacts\row_11_text.txt</t>
         </is>
       </c>
     </row>
